--- a/studySpecific/ENSEMBLE/基本設計書_CombineProcess.xlsx
+++ b/studySpecific/ENSEMBLE/基本設計書_CombineProcess.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Local\iTMS\SDTM_ENSEMBLE\studySpecific\ENSEMBLE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5B8A44-BCFD-46F1-BF89-1D8D93F7BB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722150E4-9240-40E4-9158-1011EFA3A49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -531,7 +531,367 @@
     <t>SDTM_ENSEMBLE マッピング仕様書</t>
   </si>
   <si>
+    <t>要件定義書 (RD-ENSEMBLE-001)
+詳細設計書 (DD-ENSEMBLE-001)</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>本モジュールは、ENSEMBLE研究における研究固有データ前処理を担う。</t>
+  </si>
+  <si>
+    <t>本書はブラックボックス視点で、関数単位の入出力責務と処理ルールを定義する。</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>対応要件ID</t>
+  </si>
+  <si>
+    <t>FR-01, FR-02, FR-03</t>
+  </si>
+  <si>
+    <t>任意データセットから条件一致レコードを抽出する。</t>
+  </si>
+  <si>
+    <t>FR-04, FR-05, FR-06, FR-07</t>
+  </si>
+  <si>
+    <t>RGST/LSVDAT/OC を統合し DM 情報を生成する。</t>
+  </si>
+  <si>
+    <t>F-03</t>
+  </si>
+  <si>
+    <t>FR-08, FR-09</t>
+  </si>
+  <si>
+    <t>3.1 関数公開方針</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>3.2 呼び出し責務</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> ・モジュール公開関数は </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>filter_df_by_field, DM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> を基本とする。</t>
+    </r>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> ・本モジュールは抽出・統合・導出の責務を持つ。</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> ・返却値は後続処理で扱える DataFrame 形式とする。</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>4. 入出力仕様</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>4.1 汎用データ抽出 (F-01)</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>4.2 基本情報生成 (F-02)</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>補足: RGST由来の追加列保持を許容</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>4. 処理ルール</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>R-04: 連携ルール</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> ・変更時は RD/DD/トレーサビリティ文書を同時更新する。</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>6. 要件トレーサビリティ</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>日付</t>
+  </si>
+  <si>
+    <t>変更内容</t>
+  </si>
+  <si>
+    <t>担当者</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>VC_BC05 コード初版作成 (機能起点)</t>
+  </si>
+  <si>
     <t>張　泊江（Group A）</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>VC_BC05 コード追補</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>設計文書初版作成 (RD/BD/DD)</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>VC_BC05 モジュール連動に合わせ文書更新</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>設計文書リファクタリング</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>要件ID</t>
+  </si>
+  <si>
+    <t>基本設計対応</t>
+  </si>
+  <si>
+    <t>ルール</t>
+  </si>
+  <si>
+    <t>受入観点</t>
+  </si>
+  <si>
+    <t>FR-01</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>条件抽出が成立する</t>
+  </si>
+  <si>
+    <t>FR-02</t>
+  </si>
+  <si>
+    <t>全空列が除去される</t>
+  </si>
+  <si>
+    <t>FR-03</t>
+  </si>
+  <si>
+    <t>全列文字列型で返却される</t>
+  </si>
+  <si>
+    <t>FR-04</t>
+  </si>
+  <si>
+    <t>RGST/LSVDAT/OC の統合が成立する</t>
+  </si>
+  <si>
+    <t>FR-05</t>
+  </si>
+  <si>
+    <t>R-01</t>
+  </si>
+  <si>
+    <t>RFENDAT 優先順位が一致する</t>
+  </si>
+  <si>
+    <t>FR-06</t>
+  </si>
+  <si>
+    <t>R-02</t>
+  </si>
+  <si>
+    <t>DTHFLG 判定が一致する</t>
+  </si>
+  <si>
+    <t>FR-07</t>
+  </si>
+  <si>
+    <t>R-03</t>
+  </si>
+  <si>
+    <t>不整合通知が確認できる</t>
+  </si>
+  <si>
+    <t>FR-08</t>
+  </si>
+  <si>
+    <t>R-04</t>
+  </si>
+  <si>
+    <t>FR-09</t>
+  </si>
+  <si>
+    <t>文書間追跡が欠落しない</t>
+  </si>
+  <si>
+    <t>7. 設計レビュー観点</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <r>
+      <t>1. 要件整合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>: 全FRが機能IDまたはルールに紐づくこと。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. 責務分離</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>: 呼び出し責務と変換責務が混在しないこと。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. データ契約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>: 必須出力列と導出規則が一貫すること。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. 追跡性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF333333"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>: DDとテストIDへ遷移可能であること。</t>
+    </r>
+  </si>
+  <si>
+    <t>Git Commit</t>
+  </si>
+  <si>
+    <t>09ffaf8</t>
+  </si>
+  <si>
+    <t>8c60da9</t>
+  </si>
+  <si>
+    <t>c8d9201</t>
+  </si>
+  <si>
+    <t>01d23e6</t>
+  </si>
+  <si>
+    <t>e449ccc</t>
+  </si>
+  <si>
+    <t>8. 変更履歴</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>対象機能群</t>
+  </si>
+  <si>
+    <t>filter_df_by_field, DM</t>
+  </si>
+  <si>
+    <t>入力整形工程から標準マッピング工程の間で、設定ファイルのみでは不足する処理を補完し、後続処理へ引き渡す。</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>工程連携</t>
+  </si>
+  <si>
+    <t>上位工程呼び出し連携</t>
+  </si>
+  <si>
+    <t>上位工程から研究固有関数を利用可能にする。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ・研究固有関数は上位工程から呼び出し可能であること。</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> ・呼び出し元（上位工程側）は入力データの読込責務を持つ。</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> ・本機能群は前後工程間の研究固有拡張点として利用される。</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>上位工程から呼び出せる</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>要件ID連携・連携ルール・追跡性整備に加え、基本設計段階を実装非依存化（関数名中心、モジュール/ファイル名および上下流実装参照を除外）してWIP変更を統合</t>
+  </si>
+  <si>
+    <t>96985d9</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>張　泊江</t>
     <rPh sb="0" eb="1">
       <t>ハリ</t>
     </rPh>
@@ -542,365 +902,6 @@
       <t>エ</t>
     </rPh>
     <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>要件定義書 (RD-ENSEMBLE-001)
-詳細設計書 (DD-ENSEMBLE-001)</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>本モジュールは、ENSEMBLE研究における研究固有データ前処理を担う。</t>
-  </si>
-  <si>
-    <t>本書はブラックボックス視点で、関数単位の入出力責務と処理ルールを定義する。</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>対応要件ID</t>
-  </si>
-  <si>
-    <t>FR-01, FR-02, FR-03</t>
-  </si>
-  <si>
-    <t>任意データセットから条件一致レコードを抽出する。</t>
-  </si>
-  <si>
-    <t>FR-04, FR-05, FR-06, FR-07</t>
-  </si>
-  <si>
-    <t>RGST/LSVDAT/OC を統合し DM 情報を生成する。</t>
-  </si>
-  <si>
-    <t>F-03</t>
-  </si>
-  <si>
-    <t>FR-08, FR-09</t>
-  </si>
-  <si>
-    <t>3.1 関数公開方針</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>3.2 呼び出し責務</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> ・モジュール公開関数は </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>filter_df_by_field, DM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> を基本とする。</t>
-    </r>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> ・本モジュールは抽出・統合・導出の責務を持つ。</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> ・返却値は後続処理で扱える DataFrame 形式とする。</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>4. 入出力仕様</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>4.1 汎用データ抽出 (F-01)</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>4.2 基本情報生成 (F-02)</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>補足: RGST由来の追加列保持を許容</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>4. 処理ルール</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>R-04: 連携ルール</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> ・変更時は RD/DD/トレーサビリティ文書を同時更新する。</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>6. 要件トレーサビリティ</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>日付</t>
-  </si>
-  <si>
-    <t>変更内容</t>
-  </si>
-  <si>
-    <t>担当者</t>
-  </si>
-  <si>
-    <t>0.1</t>
-  </si>
-  <si>
-    <t>VC_BC05 コード初版作成 (機能起点)</t>
-  </si>
-  <si>
-    <t>張　泊江（Group A）</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>0.2</t>
-  </si>
-  <si>
-    <t>VC_BC05 コード追補</t>
-  </si>
-  <si>
-    <t>1.0</t>
-  </si>
-  <si>
-    <t>設計文書初版作成 (RD/BD/DD)</t>
-  </si>
-  <si>
-    <t>1.1</t>
-  </si>
-  <si>
-    <t>VC_BC05 モジュール連動に合わせ文書更新</t>
-  </si>
-  <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>設計文書リファクタリング</t>
-  </si>
-  <si>
-    <t>1.3</t>
-  </si>
-  <si>
-    <t>要件ID</t>
-  </si>
-  <si>
-    <t>基本設計対応</t>
-  </si>
-  <si>
-    <t>ルール</t>
-  </si>
-  <si>
-    <t>受入観点</t>
-  </si>
-  <si>
-    <t>FR-01</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>条件抽出が成立する</t>
-  </si>
-  <si>
-    <t>FR-02</t>
-  </si>
-  <si>
-    <t>全空列が除去される</t>
-  </si>
-  <si>
-    <t>FR-03</t>
-  </si>
-  <si>
-    <t>全列文字列型で返却される</t>
-  </si>
-  <si>
-    <t>FR-04</t>
-  </si>
-  <si>
-    <t>RGST/LSVDAT/OC の統合が成立する</t>
-  </si>
-  <si>
-    <t>FR-05</t>
-  </si>
-  <si>
-    <t>R-01</t>
-  </si>
-  <si>
-    <t>RFENDAT 優先順位が一致する</t>
-  </si>
-  <si>
-    <t>FR-06</t>
-  </si>
-  <si>
-    <t>R-02</t>
-  </si>
-  <si>
-    <t>DTHFLG 判定が一致する</t>
-  </si>
-  <si>
-    <t>FR-07</t>
-  </si>
-  <si>
-    <t>R-03</t>
-  </si>
-  <si>
-    <t>不整合通知が確認できる</t>
-  </si>
-  <si>
-    <t>FR-08</t>
-  </si>
-  <si>
-    <t>R-04</t>
-  </si>
-  <si>
-    <t>FR-09</t>
-  </si>
-  <si>
-    <t>文書間追跡が欠落しない</t>
-  </si>
-  <si>
-    <t>7. 設計レビュー観点</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <r>
-      <t>1. 要件整合</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF333333"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>: 全FRが機能IDまたはルールに紐づくこと。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>2. 責務分離</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF333333"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>: 呼び出し責務と変換責務が混在しないこと。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>3. データ契約</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF333333"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>: 必須出力列と導出規則が一貫すること。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>4. 追跡性</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF333333"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>: DDとテストIDへ遷移可能であること。</t>
-    </r>
-  </si>
-  <si>
-    <t>Git Commit</t>
-  </si>
-  <si>
-    <t>09ffaf8</t>
-  </si>
-  <si>
-    <t>8c60da9</t>
-  </si>
-  <si>
-    <t>c8d9201</t>
-  </si>
-  <si>
-    <t>01d23e6</t>
-  </si>
-  <si>
-    <t>e449ccc</t>
-  </si>
-  <si>
-    <t>WIP</t>
-  </si>
-  <si>
-    <t>8. 変更履歴</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>対象機能群</t>
-  </si>
-  <si>
-    <t>filter_df_by_field, DM</t>
-  </si>
-  <si>
-    <t>入力整形工程から標準マッピング工程の間で、設定ファイルのみでは不足する処理を補完し、後続処理へ引き渡す。</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>工程連携</t>
-  </si>
-  <si>
-    <t>上位工程呼び出し連携</t>
-  </si>
-  <si>
-    <t>上位工程から研究固有関数を利用可能にする。</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ・研究固有関数は上位工程から呼び出し可能であること。</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> ・呼び出し元（上位工程側）は入力データの読込責務を持つ。</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> ・本機能群は前後工程間の研究固有拡張点として利用される。</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>上位工程から呼び出せる</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>要件ID連携・連携ルール・追跡性整備に加え、基本設計段階を実装非依存化（関数名中心、モジュール/ファイル名および上下流実装参照を除外）してWIP変更を統合</t>
   </si>
 </sst>
 </file>
@@ -1181,20 +1182,20 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1560,7 +1561,7 @@
         <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>81</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.15">
@@ -1593,10 +1594,10 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.15">
       <c r="B17" s="13" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="27" x14ac:dyDescent="0.15">
@@ -1604,7 +1605,7 @@
         <v>10</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1628,17 +1629,17 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1682,7 +1683,7 @@
         <v>14</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>15</v>
@@ -1702,10 +1703,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>86</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
@@ -1722,10 +1723,10 @@
         <v>21</v>
       </c>
       <c r="E5" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>88</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
@@ -1733,19 +1734,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="E6" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="F6" s="13" t="s">
         <v>162</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -1772,42 +1773,42 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A3" s="32" t="s">
-        <v>92</v>
-      </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
+      <c r="A3" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A7" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
+      <c r="A7" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1834,22 +1835,22 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A3" s="35" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A3" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
@@ -1862,11 +1863,11 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
@@ -1884,11 +1885,11 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A12" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
+      <c r="A12" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A14" s="10" t="s">
@@ -2007,7 +2008,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A29" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2034,7 +2035,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.15">
@@ -2043,19 +2044,19 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="10" t="s">
@@ -2093,19 +2094,19 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A17" s="11" t="s">
@@ -2128,19 +2129,19 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A22" s="32" t="s">
+      <c r="A22" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A24" s="11" t="s">
@@ -2153,28 +2154,28 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A27" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
+      <c r="A27" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="35"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A29" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -2202,147 +2203,147 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>122</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" s="22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B4" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>125</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" s="24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" s="25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B7" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" s="25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B8" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" s="25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B9" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>137</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B10" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>140</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>143</v>
-      </c>
       <c r="D11" s="13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="D12" s="13" t="s">
         <v>144</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2362,27 +2363,27 @@
   <sheetData>
     <row r="1" spans="1:1" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A1" s="26" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="28" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="28" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="28" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2405,7 +2406,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A1" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
@@ -2413,118 +2414,118 @@
         <v>74</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>107</v>
-      </c>
       <c r="E3" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="30" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A4" s="22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B4" s="23">
         <v>46055</v>
       </c>
       <c r="C4" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>110</v>
-      </c>
       <c r="E4" s="16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="30" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B5" s="23">
         <v>46055</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="30" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A6" s="24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B6" s="23">
         <v>46066</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" s="23">
         <v>46066</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B8" s="23">
         <v>46066</v>
       </c>
       <c r="C8" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="27" x14ac:dyDescent="0.15">
+      <c r="A9" s="32" t="s">
         <v>118</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="27" x14ac:dyDescent="0.15">
-      <c r="A9" s="34" t="s">
-        <v>119</v>
       </c>
       <c r="B9" s="23">
         <v>46073</v>
       </c>
-      <c r="C9" s="35" t="s">
-        <v>169</v>
+      <c r="C9" s="33" t="s">
+        <v>167</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="E9" s="36" t="s">
-        <v>157</v>
+        <v>109</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
